--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-23 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-22 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.712</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>262.79</v>
+        <v>251.23</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>128.04</v>
+        <v>141.18</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.052</v>
+        <v>0.78</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.737</v>
+        <v>0.671</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.667</v>
+        <v>0.444</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.0473799991607666</v>
+        <v>0.04963000297546387</v>
       </c>
     </row>
     <row r="6">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>2675000064</v>
+        <v>2704999936</v>
       </c>
     </row>
     <row r="33">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>109000000</v>
+        <v>126000000</v>
       </c>
     </row>
     <row r="34">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>42276816.49484536</v>
+        <v>41897633.09250602</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>128.04</v>
+        <v>141.18</v>
       </c>
     </row>
     <row r="38">
@@ -1520,196 +1520,208 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>5413123584</v>
+        <v>5915107840</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>14.4</v>
+        <v>16.47</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>10.83</v>
+        <v>11.03</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AVT</t>
+          <t>AMTM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Avnet, Inc.</t>
+          <t>Amentum Holdings, Inc.</t>
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>7274948608</v>
+        <v>5068617728</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.104736</v>
+        <v>24.975904</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>11.222</v>
+        <v>8.337</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>0.383</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Concentrix Corporation</t>
+          <t>Booz Allen Hamilton Holding Cor</t>
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>1549866112</v>
-      </c>
-      <c r="D7" s="34" t="n"/>
+        <v>9462818816</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>12.369496</v>
+      </c>
       <c r="E7" s="34" t="n">
-        <v>5.334</v>
+        <v>10.077</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.68</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>CACI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DLocal Limited</t>
+          <t>CACI International, Inc.</t>
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>4464062464</v>
+        <v>13599539200</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>22.308823</v>
+        <v>25.2617</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>14.555</v>
+        <v>15.953</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>2.628</v>
+        <v>1.982</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INGM</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ingram Micro Holding Corporatio</t>
+          <t xml:space="preserve">Huntington Ingalls Industries, </t>
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>6343202304</v>
+        <v>10883156992</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>15.027322</v>
+        <v>16.459475</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>7.696</v>
+        <v>11.725</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.175</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NIQ Global Intelligence plc</t>
+          <t>ICF International, Inc.</t>
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>5539271680</v>
-      </c>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="34" t="n"/>
-      <c r="F10" s="34" t="n"/>
+        <v>1649020544</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>19.037268</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>11.027</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>1.193</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAY</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Paymentus Holdings, Inc.</t>
+          <t>KBR, Inc.</t>
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>5037585920</v>
+        <v>4899623424</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>60.60606</v>
+        <v>11.671172</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>43.15</v>
+        <v>10.66</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.433</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PSFE</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paysafe Limited</t>
+          <t>Leidos Holdings, Inc.</t>
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>358720288</v>
-      </c>
-      <c r="D12" s="34" t="n"/>
+        <v>16708032512</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <v>12.431373</v>
+      </c>
       <c r="E12" s="34" t="n">
-        <v>6.936</v>
+        <v>9.278</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.52</v>
+        <v>1.253</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>PSN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Silicon Laboratories, Inc.</t>
+          <t>Parsons Corporation</t>
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>7273953792</v>
-      </c>
-      <c r="D13" s="34" t="n"/>
+        <v>5010775040</v>
+      </c>
+      <c r="D13" s="34" t="n">
+        <v>32.35517</v>
+      </c>
       <c r="E13" s="34" t="n">
-        <v>-689.187</v>
+        <v>13.484</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>8.035</v>
+        <v>1.008</v>
       </c>
     </row>
     <row r="15">
@@ -1757,13 +1769,13 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">

--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-22 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-23 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.712</v>
+        <v>0.706</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>251.23</v>
+        <v>249.56</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>141.18</v>
+        <v>145.78</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.78</v>
+        <v>0.712</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.671</v>
+        <v>0.643</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04963000297546387</v>
+        <v>0.04991999626159668</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>41897633.09250602</v>
+        <v>41897636.43846893</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>141.18</v>
+        <v>145.78</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>5915107840</v>
+        <v>6107837440</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>16.47</v>
+        <v>17.01</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>11.03</v>
+        <v>11.41</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>5068617728</v>
+        <v>5269112832</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>24.975904</v>
+        <v>25.963856</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.337</v>
+        <v>8.614000000000001</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>0.594</v>
+        <v>0.613</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>9462818816</v>
+        <v>9409292288</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>12.369496</v>
+        <v>12.299528</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>10.077</v>
+        <v>10.415</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>1.14</v>
+        <v>1.178</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>13599539200</v>
+        <v>14035452928</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>25.2617</v>
+        <v>26.071426</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>15.953</v>
+        <v>14.96</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>1.982</v>
+        <v>1.916</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>10883156992</v>
+        <v>10812819456</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>16.459475</v>
+        <v>16.353098</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>11.725</v>
+        <v>11.89</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.04</v>
+        <v>1.055</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>1649020544</v>
+        <v>1692420736</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>19.037268</v>
+        <v>19.538303</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>11.027</v>
+        <v>11.335</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>1.193</v>
+        <v>1.227</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>4899623424</v>
+        <v>4956983808</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>11.671172</v>
+        <v>11.807808</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>10.66</v>
+        <v>11.075</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>0.93</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>16708032512</v>
+        <v>17099567104</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>12.431373</v>
+        <v>12.722689</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>9.278</v>
+        <v>9.567</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.253</v>
+        <v>1.292</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>5010775040</v>
+        <v>5202490368</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>32.35517</v>
+        <v>33.5931</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>13.484</v>
+        <v>14.029</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>1.008</v>
+        <v>1.049</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-23 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-24 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>249.56</v>
+        <v>249.79</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>145.78</v>
+        <v>145.73</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.712</v>
+        <v>0.714</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04991999626159668</v>
+        <v>0.0498799991607666</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>41897636.43846893</v>
+        <v>41897634.91388184</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>145.78</v>
+        <v>145.73</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>6107837440</v>
+        <v>6105742336</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>17.01</v>
+        <v>17</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>11.41</v>
+        <v>11.53</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>5269112832</v>
+        <v>5320459776</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>25.963856</v>
+        <v>26.216867</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.614000000000001</v>
+        <v>8.728</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>0.613</v>
+        <v>0.621</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>9409292288</v>
+        <v>9327674368</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>12.299528</v>
+        <v>12.3144655</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>10.415</v>
+        <v>11.135</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>1.178</v>
+        <v>1.244</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>14035452928</v>
+        <v>14010701824</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>26.071426</v>
+        <v>26.02545</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>14.96</v>
+        <v>15.276</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>1.916</v>
+        <v>1.956</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>10812819456</v>
+        <v>10800012288</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>16.353098</v>
+        <v>16.333729</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>11.89</v>
+        <v>11.729</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.055</v>
+        <v>1.041</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>1692420736</v>
+        <v>1692958720</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>19.538303</v>
+        <v>19.544514</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>11.335</v>
+        <v>11.432</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>1.227</v>
+        <v>1.237</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>4956983808</v>
+        <v>4945637888</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>11.807808</v>
+        <v>11.780781</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>11.075</v>
+        <v>11.019</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>0.967</v>
+        <v>0.962</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>17099567104</v>
+        <v>17076979712</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>12.722689</v>
+        <v>12.705882</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>9.567</v>
+        <v>9.638999999999999</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.292</v>
+        <v>1.302</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>5202490368</v>
+        <v>5237736448</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>33.5931</v>
+        <v>33.82069</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>14.029</v>
+        <v>14.311</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>1.049</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-24 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-25 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-25 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-31 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.706</v>
+        <v>0.721</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>249.79</v>
+        <v>253.22</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>145.73</v>
+        <v>151.86</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.643</v>
+        <v>0.605</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.444</v>
+        <v>0.5</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.0498799991607666</v>
+        <v>0.04928999900817871</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>41897634.91388184</v>
+        <v>41897634.97958646</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>145.73</v>
+        <v>151.86</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>6105742336</v>
+        <v>6362574848</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>17</v>
+        <v>17.72</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>11.53</v>
+        <v>11.88</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>5320459776</v>
+        <v>5347355648</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>26.216867</v>
+        <v>26.3494</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.728</v>
+        <v>8.755000000000001</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>0.621</v>
+        <v>0.623</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>9327674368</v>
+        <v>10538890240</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>12.3144655</v>
+        <v>13.740683</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>11.135</v>
+        <v>12.118</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>1.244</v>
+        <v>1.354</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>14010701824</v>
+        <v>14930928640</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>26.02545</v>
+        <v>27.73481</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>15.276</v>
+        <v>16.017</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>1.956</v>
+        <v>2.051</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>10800012288</v>
+        <v>12486992896</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>16.333729</v>
+        <v>17.064083</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>11.729</v>
+        <v>12.11</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.041</v>
+        <v>1.111</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>1692958720</v>
+        <v>1712327296</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>19.544514</v>
+        <v>19.768116</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>11.432</v>
+        <v>11.53</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>1.237</v>
+        <v>1.248</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>4945637888</v>
+        <v>4880417792</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>11.780781</v>
+        <v>11.25</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>11.019</v>
+        <v>10.386</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>0.962</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>17076979712</v>
+        <v>17942876160</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>12.705882</v>
+        <v>13.35014</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>9.638999999999999</v>
+        <v>10.002</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.302</v>
+        <v>1.351</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>5237736448</v>
+        <v>5349765632</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>33.82069</v>
+        <v>37.272057</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>14.311</v>
+        <v>14.22</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>1.07</v>
+        <v>1.061</v>
       </c>
     </row>
     <row r="15">
@@ -1772,7 +1772,7 @@
         <v>0.5</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="36" t="n">
         <v>0.5</v>
